--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260730.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260730.xlsx
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,316,000</t>
+          <t>963,659</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>963,659</t>
+          <t>3,316,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,886,000</t>
+          <t>5,888,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2,672,703</t>
+          <t>3,581,981</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,581,981</t>
+          <t>1,886,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>5,888,000</t>
+          <t>2,672,703</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,419,384</t>
+          <t>1,231,441</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,231,441</t>
+          <t>150,386</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>150,386</t>
+          <t>1,419,384</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>10,910,121</t>
+          <t>46,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>46,000</t>
+          <t>10,910,121</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,104,956</t>
+          <t>799,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>828,000</t>
+          <t>299,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>799,000</t>
+          <t>5,104,956</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>299,000</t>
+          <t>828,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,032,121</t>
+          <t>96,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>118,000</t>
+          <t>187,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>187,000</t>
+          <t>118,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>1,032,121</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>512,000</t>
+          <t>401,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>234,000</t>
+          <t>512,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>401,000</t>
+          <t>234,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>67,538</t>
+          <t>341,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>341,000</t>
+          <t>67,538</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>161,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>183,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>161,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>183,000</t>
+          <t>261,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>261,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
